--- a/Practice exams.xlsx
+++ b/Practice exams.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/AdrianL/Documents/Medtrainer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F6382B-C59B-8046-B0BF-4927E4E6D14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC40BB4D-8172-8D4A-ACF4-38C4CA01F4F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="640" windowWidth="14400" windowHeight="17380" xr2:uid="{C8BA863C-0E31-FA49-AA6C-620A11778D1A}"/>
+    <workbookView xWindow="14420" yWindow="640" windowWidth="14400" windowHeight="17380" activeTab="1" xr2:uid="{C8BA863C-0E31-FA49-AA6C-620A11778D1A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="2019 e1" sheetId="1" r:id="rId1"/>
+    <sheet name="2026 paper" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="21">
   <si>
     <t>A</t>
   </si>
@@ -1751,4 +1752,374 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC3296B6-ED33-3142-8D0A-56374F7E9200}">
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1">
+        <f t="shared" ref="C1:C19" si="0">IF(A1=B1,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <f>IF(A20=B20,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <f>IF(A21=B21,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22">
+        <f>IF(A22=B22,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23">
+        <f>IF(A23=B23,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24">
+        <f>IF(A24=B24,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <f>IF(A25=B25,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26">
+        <f>IF(A26=B26,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <f>IF(A27=B27,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28">
+        <f>IF(A28=B28,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29">
+        <f>IF(A29=B29,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <f>IF(A30=B30,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>